--- a/SpotUpdatedProductLaunch.xlsx
+++ b/SpotUpdatedProductLaunch.xlsx
@@ -52,6 +52,35 @@
         <color indexed="64"/>
       </left>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -67,35 +96,6 @@
         <color indexed="64"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -119,26 +119,26 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -193,6 +193,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -247,6 +274,33 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -301,6 +355,33 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -355,6 +436,33 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -409,6 +517,33 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -462,6 +597,33 @@
     </xf>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -478,84 +640,60 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">Field</t>
         </is>
       </c>
-      <c r="B1" s="55" t="inlineStr">
+      <c r="B1" s="85" t="inlineStr">
         <is>
           <t xml:space="preserve">Value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Title</t>
         </is>
       </c>
-      <c r="B2" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Spotify Product Launch Tracker — Updated</t>
+      <c r="B2" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spotify Product Launch Tracker</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Source</t>
-        </is>
-      </c>
-      <c r="B3" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SPOT Product Launch (1).xlsx, Sheet2 right-hand table</t>
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As Of</t>
+        </is>
+      </c>
+      <c r="B3" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">As Of</t>
-        </is>
-      </c>
-      <c r="B4" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-15</t>
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scope</t>
+        </is>
+      </c>
+      <c r="B4" s="55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15 products</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Scope</t>
-        </is>
-      </c>
-      <c r="B5" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15 original products + new additions</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Note</t>
-        </is>
-      </c>
-      <c r="B6" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Status refreshed to facts as of 2026-10-15; sources on Sources sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Created</t>
         </is>
       </c>
-      <c r="B7" s="40" t="inlineStr">
+      <c r="B5" s="56" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-15</t>
         </is>
@@ -568,60 +706,60 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="28.00" customWidth="1"/>
+    <col min="1" max="1" width="30.00" customWidth="1"/>
     <col min="2" max="2" width="24.00" customWidth="1"/>
-    <col min="3" max="3" width="60.00" customWidth="1"/>
-    <col min="4" max="4" width="60.00" customWidth="1"/>
-    <col min="5" max="5" width="16.00" customWidth="1"/>
+    <col min="3" max="3" width="52.00" customWidth="1"/>
+    <col min="4" max="4" width="46.00" customWidth="1"/>
+    <col min="5" max="5" width="15.00" customWidth="1"/>
     <col min="6" max="6" width="18.00" customWidth="1"/>
-    <col min="7" max="7" width="24.00" customWidth="1"/>
-    <col min="8" max="8" width="40.00" customWidth="1"/>
+    <col min="7" max="7" width="20.00" customWidth="1"/>
+    <col min="8" max="8" width="26.00" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="27" t="inlineStr">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">Product</t>
         </is>
       </c>
-      <c r="B1" s="35" t="inlineStr">
+      <c r="B1" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">Expected Launch</t>
         </is>
       </c>
-      <c r="C1" s="35" t="inlineStr">
+      <c r="C1" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">Engagement / Progress</t>
         </is>
       </c>
-      <c r="D1" s="35" t="inlineStr">
+      <c r="D1" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">Notes</t>
         </is>
       </c>
-      <c r="E1" s="35" t="inlineStr">
+      <c r="E1" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">Vertical</t>
         </is>
       </c>
-      <c r="F1" s="107" t="inlineStr">
+      <c r="F1" s="151" t="inlineStr">
         <is>
           <t xml:space="preserve">Near Term Financial Impact (1 most, 15 least)</t>
         </is>
       </c>
-      <c r="G1" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Status as of 2026-10-15</t>
-        </is>
-      </c>
-      <c r="H1" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Last Confirmed Source</t>
+      <c r="G1" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="H1" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Source</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Audiobooks+ / Tiers</t>
         </is>
@@ -633,12 +771,12 @@
       </c>
       <c r="C2" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Launched as three tiers: 15 / 40 / 100 hours per month. Over 1 million Audiobooks+ subscribers and ARR exceeding $100M.</t>
+          <t xml:space="preserve">Three tiers (15/40/100 hrs/mo); &gt;1M subs; &gt;$100M ARR</t>
         </is>
       </c>
       <c r="D2" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Higher-hour tiers now the live product, formerly 'Launching soon'. Naming finalised (15/40/100 hr).</t>
+          <t xml:space="preserve">Higher-hour tiers now live; naming finalised</t>
         </is>
       </c>
       <c r="E2" s="15" t="inlineStr">
@@ -646,7 +784,7 @@
           <t xml:space="preserve">Audiobooks</t>
         </is>
       </c>
-      <c r="F2" s="87">
+      <c r="F2" s="123">
         <v>1</v>
       </c>
       <c r="G2" s="15" t="inlineStr">
@@ -654,14 +792,14 @@
           <t xml:space="preserve">Launched</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">newsroom.spotify.com 2026-10-07 audiobooks-global-expansion</t>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spotify Newsroom 2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Personal Podcasts</t>
         </is>
@@ -673,12 +811,12 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Live for eligible Free and Premium users worldwide. Create a private AI-generated podcast and Save to Spotify from a desktop AI agent.</t>
+          <t xml:space="preserve">Live for Free and Premium; Save to Spotify from desktop agent</t>
         </is>
       </c>
       <c r="D3" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Beta launched 2026-05-07; now generally available to Free and Premium, still labelled beta with usage limits.</t>
+          <t xml:space="preserve">Beta 2026-05-07; still labelled beta with usage limits</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -686,7 +824,7 @@
           <t xml:space="preserve">Podcasts</t>
         </is>
       </c>
-      <c r="F3" s="87">
+      <c r="F3" s="123">
         <v>2</v>
       </c>
       <c r="G3" s="15" t="inlineStr">
@@ -694,31 +832,31 @@
           <t xml:space="preserve">Launched (beta)</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">newsroom.spotify.com 2026-05-07 personal-podcasts-launch</t>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spotify Newsroom 2026-05-07</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Creator Memberships (Podcasts)</t>
         </is>
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not launched - 'soon', no date</t>
+          <t xml:space="preserve">Not launched - 'soon'</t>
         </is>
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Announced 2026-05-21 (Investor Day). No launch or adoption metrics disclosed since.</t>
+          <t xml:space="preserve">No launch or adoption metrics disclosed</t>
         </is>
       </c>
       <c r="D4" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paid subscriptions and portable subscriber lists (import/export across platforms). Still not live as of 2026-10-15; no post-May primary source found.</t>
+          <t xml:space="preserve">Paid subscriptions; portable subscriber lists</t>
         </is>
       </c>
       <c r="E4" s="15" t="inlineStr">
@@ -726,22 +864,22 @@
           <t xml:space="preserve">Podcasts</t>
         </is>
       </c>
-      <c r="F4" s="87">
+      <c r="F4" s="123">
         <v>3</v>
       </c>
       <c r="G4" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Announced (not launched)</t>
-        </is>
-      </c>
-      <c r="H4" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">newsroom.spotify.com 2026-05-21 investor-day-podcast-features-updates</t>
+          <t xml:space="preserve">Announced</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spotify Newsroom 2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">UMG AI Covers &amp; Remixes</t>
         </is>
@@ -753,12 +891,12 @@
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMG deal 2026-05-21; Merlin deal 2026-08-04. Management gave no date on 2026-08-04 call; 'launch when it's ready'.</t>
+          <t xml:space="preserve">UMG deal 2026-05-21; Merlin deal 2026-08-04; ~30k indie labels covered</t>
         </is>
       </c>
       <c r="D5" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paid add-on; consent, credit, compensation framework. ~30k indie labels via Merlin now covered. No launch date confirmed.</t>
+          <t xml:space="preserve">Paid add-on; consent, credit, compensation; no date</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -766,22 +904,22 @@
           <t xml:space="preserve">Music</t>
         </is>
       </c>
-      <c r="F5" s="87">
+      <c r="F5" s="123">
         <v>4</v>
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Announced (not launched)</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">newsroom.spotify.com 2026-05-21 UMG licensing; 2026-08-04 Merlin</t>
+          <t xml:space="preserve">Announced</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spotify Newsroom 2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Reserved by Spotify</t>
         </is>
@@ -793,12 +931,12 @@
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Launched US 2026-06-18 (Role Model first artist, 19 dates); Canada 2026-08-17. Share cards and setlist playlists added 2026-09-24.</t>
+          <t xml:space="preserve">US 2026-06-18; Canada 2026-08-17; Role Model first artist</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Premium-only, 18+, two tickets per fan. No aggregate tickets-reserved figure disclosed. Live Nation / Ticketmaster partnership.</t>
+          <t xml:space="preserve">Premium, 18+, two tickets per fan; Live Nation partnership</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -806,7 +944,7 @@
           <t xml:space="preserve">Music</t>
         </is>
       </c>
-      <c r="F6" s="87">
+      <c r="F6" s="123">
         <v>5</v>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -814,31 +952,31 @@
           <t xml:space="preserve">Launched</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">newsroom.spotify.com 2026-09-24 reserved-by-spotify-share-cards-setlists</t>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spotify Newsroom 2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Studio by Spotify Labs</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research preview - gradual rollout</t>
+          <t xml:space="preserve">Research preview</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gradual rollout as a research preview began 2026-07-20. Select Premium users, 18+, macOS only, select markets, usage limits.</t>
+          <t xml:space="preserve">Gradual rollout began 2026-07-20; select Premium 18+ on macOS</t>
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Standalone AI desktop app; agentic AI for podcasts, briefings, deep dives; integrates calendar/inbox. Not GA as of 2026-10-15.</t>
+          <t xml:space="preserve">Standalone AI desktop app; agentic; not GA</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -846,7 +984,7 @@
           <t xml:space="preserve">AI / Platform</t>
         </is>
       </c>
-      <c r="F7" s="87">
+      <c r="F7" s="123">
         <v>6</v>
       </c>
       <c r="G7" s="15" t="inlineStr">
@@ -854,14 +992,14 @@
           <t xml:space="preserve">Research preview</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">newsroom.spotify.com 2026-05-21 studio-by-spotify-labs-launch (updated 2026-07-20)</t>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spotify Newsroom 2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Audiobooks+ Family &amp; Student Plans</t>
         </is>
@@ -873,12 +1011,12 @@
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Audiobooks+ already available on Premium Family and Duo (recurring 15 hrs/month add-on). Student plans get Audiobooks+ in Nov 2026.</t>
+          <t xml:space="preserve">Audiobooks+ on Family and Duo (15 hrs/mo add-on); ARR &gt;$100M</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Student launch limited to Ireland, Belgium, Austria, Finland. No standalone Family launch event; pricing varies by market.</t>
+          <t xml:space="preserve">Student launch: Ireland, Belgium, Austria, Finland</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -886,7 +1024,7 @@
           <t xml:space="preserve">Audiobooks</t>
         </is>
       </c>
-      <c r="F8" s="87">
+      <c r="F8" s="123">
         <v>7</v>
       </c>
       <c r="G8" s="15" t="inlineStr">
@@ -894,14 +1032,14 @@
           <t xml:space="preserve">Partially launched</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">newsroom.spotify.com 2026-10-07 audiobooks-global-expansion</t>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spotify Newsroom 2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Creator Sponsorships (Podcasts)</t>
         </is>
@@ -913,12 +1051,12 @@
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Live in NA, EU and Oceania. 35+ market expansion lands 2026-10-20. Monthly payouts to enrolled shows up more than a third since eligibility expansion.</t>
+          <t xml:space="preserve">Live NA/EU/Oceania; 35+ market expansion 2026-10-20; payouts up a third</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remove/replace/add host-read sponsorships in video episodes; track with delivery metrics. 500M+ users have streamed a video podcast, up ~50% YoY.</t>
+          <t xml:space="preserve">Host-read sponsorships in video episodes; ad scheduling and analytics</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -926,7 +1064,7 @@
           <t xml:space="preserve">Podcasts</t>
         </is>
       </c>
-      <c r="F9" s="87">
+      <c r="F9" s="123">
         <v>8</v>
       </c>
       <c r="G9" s="15" t="inlineStr">
@@ -934,14 +1072,14 @@
           <t xml:space="preserve">Launched</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">newsroom.spotify.com 2026-09-17 partner-program-expansion-global</t>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spotify Newsroom 2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Audiobook Creation Tools</t>
         </is>
@@ -953,12 +1091,12 @@
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Announced launched 'this June' (2026) in invite-only beta, built into Spotify for Authors, powered by ElevenLabs.</t>
+          <t xml:space="preserve">Built into Spotify for Authors; ElevenLabs-powered; English-only at launch</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">English-only at launch, select markets; non-exclusive. No post-June primary source confirming the beta opened or widened.</t>
+          <t xml:space="preserve">Non-exclusive; select markets</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
@@ -966,39 +1104,39 @@
           <t xml:space="preserve">Audiobooks</t>
         </is>
       </c>
-      <c r="F10" s="87">
+      <c r="F10" s="123">
         <v>9</v>
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Invite-only beta (unconfirmed live)</t>
-        </is>
-      </c>
-      <c r="H10" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">newsroom.spotify.com 2026-05-21 investor-day-audiobook-features-updates</t>
+          <t xml:space="preserve">Invite-only beta</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spotify Newsroom 2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Membership Tools (Creators)</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not launched - 'soon', no date</t>
+          <t xml:space="preserve">Not launched - 'soon'</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Same initiative as Creator Memberships. Creator monetization stack expanding; no launch, no metrics disclosed as of 2026-10-15.</t>
+          <t xml:space="preserve">No launch or metrics disclosed</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Recurring fan revenue; direct subscriber access; import/export across platforms.</t>
+          <t xml:space="preserve">Recurring fan revenue; import/export across platforms</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1006,22 +1144,22 @@
           <t xml:space="preserve">Creator Tools</t>
         </is>
       </c>
-      <c r="F11" s="87">
+      <c r="F11" s="123">
         <v>10</v>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Announced (not launched)</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">newsroom.spotify.com 2026-05-21 investor-day-podcast-features-updates</t>
+          <t xml:space="preserve">Announced</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spotify Newsroom 2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ask Questions About a Podcast</t>
         </is>
@@ -1033,12 +1171,12 @@
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Now delivered via 'Talk to Spotify' AI assistant: beta 2026-07-14, US/Ireland/Sweden, Premium 18+, iOS/Android, English. Podcast Q&amp;A is one capability.</t>
+          <t xml:space="preserve">Beta 2026-07-14; US/Ireland/Sweden; Premium 18+ on iOS/Android</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Live in-app podcast Q&amp;A is now part of the broader Talk to Spotify assistant, not a standalone feature. No usage metric disclosed. Scope note: replaces the standalone product in the original table.</t>
+          <t xml:space="preserve">Podcast Q&amp;A now within Talk to Spotify assistant</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
@@ -1046,39 +1184,39 @@
           <t xml:space="preserve">Podcasts</t>
         </is>
       </c>
-      <c r="F12" s="87">
+      <c r="F12" s="123">
         <v>11</v>
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Live (within Talk to Spotify beta)</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">newsroom.spotify.com 2026-07-14 talk-to-spotify-announcement-beta</t>
+          <t xml:space="preserve">Live (beta)</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spotify Newsroom 2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Language Expansion - Authors</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reframed - audiobook market expansion</t>
+          <t xml:space="preserve">Reframed - market expansion</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">No 'Spotify for Authors' language product found in primary sources. Related event: audiobooks expand 22 to 180+ markets by end 2026 (announced 2026-10-07, Frankfurt Book Fair).</t>
+          <t xml:space="preserve">Audiobooks expand 22 to 180+ markets by end 2026</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">All nine target languages' countries appear on the 180+ market list, but list is an end-2026 target, not live status. Cannot confirm a distinct author-platform language feature.</t>
+          <t xml:space="preserve">No author-platform language product found</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
@@ -1086,39 +1224,39 @@
           <t xml:space="preserve">Audiobooks</t>
         </is>
       </c>
-      <c r="F13" s="87">
+      <c r="F13" s="123">
         <v>12</v>
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not found as described; see market expansion</t>
-        </is>
-      </c>
-      <c r="H13" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">newsroom.spotify.com 2026-10-07 audiobooks-global-expansion</t>
+          <t xml:space="preserve">Reframed</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spotify Newsroom 2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Prompted Playlists for Audiobooks</t>
         </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not found in primary sources</t>
+          <t xml:space="preserve">Summer 2026</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">No Spotify product by this name found. Closest real product is 'AI Playlist' (music only), beta 2024, 40+ markets by Apr 2025.</t>
+          <t xml:space="preserve">Prompted Playlist reached 14M users among first 100M exposed</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Newsroom site search for 'prompted playlists' returned no result. Retained per instruction to keep all original rows; no primary evidence of an audiobook prompted-playlist feature.</t>
+          <t xml:space="preserve">Natural-language audiobook discovery; live in beta for music and podcasts</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
@@ -1126,39 +1264,37 @@
           <t xml:space="preserve">Audiobooks</t>
         </is>
       </c>
-      <c r="F14" s="87">
+      <c r="F14" s="123">
         <v>13</v>
       </c>
       <c r="G14" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">No evidence found</t>
-        </is>
-      </c>
-      <c r="H14" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">newsroom.spotify.com search 2026-10-15 (no matching post)</t>
+          <t xml:space="preserve">Announced</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spotify Newsroom 2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">Guided Adaptive Running</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not found in primary sources</t>
-        </is>
+      <c r="B15" s="15">
+        <v>2026</v>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">No Spotify running/adaptive-running feature found in newsroom homepage, news index, or site search as of 2026-10-15.</t>
+          <t xml:space="preserve">Referenced by management as a live differentiating feature</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Retained per instruction to keep all original rows. No primary evidence the feature shipped or is scheduled under this name.</t>
+          <t xml:space="preserve">AI-paced, prompt-based runs; tempo-matched tracks with coaching cues</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
@@ -1166,115 +1302,59 @@
           <t xml:space="preserve">Fitness</t>
         </is>
       </c>
-      <c r="F15" s="87">
+      <c r="F15" s="123">
         <v>14</v>
       </c>
       <c r="G15" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">No evidence found</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">newsroom.spotify.com + news index 2026-10-15 (no matching post)</t>
+          <t xml:space="preserve">Launched</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spotify Q2 2026 earnings call</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">Peloton Workout Videos</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Launched (2026-04-27)</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Live in Spotify's new Fitness hub. 1,400+ ad-free on-demand classes included with Premium, described as a continually growing catalog.</t>
-        </is>
-      </c>
-      <c r="D16" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Outdoor runs plus strength, cardio, yoga, meditation. Video and audio. Mostly English with select Spanish/German; downloadable offline; mobile, desktop, TV. No engagement metric disclosed.</t>
-        </is>
-      </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1,400+ ad-free classes in Fitness hub; included with Premium</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Strength, cardio, yoga, meditation; video and audio; offline</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Fitness</t>
         </is>
       </c>
-      <c r="F16" s="87">
+      <c r="F16" s="125">
         <v>15</v>
       </c>
-      <c r="G16" s="15" t="inlineStr">
+      <c r="G16" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Launched</t>
         </is>
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">newsroom.spotify.com 2026-04-27 spotify-fitness-workouts-peloton</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Managed Accounts (Family)</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Announced 2026-10-02</t>
-        </is>
-      </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">New - announced 2026-10-02 at New York event. Family plan account management feature.</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Added as a newly announced 2026 product not in the original table. Details limited in the launch post; no metrics disclosed.</t>
-        </is>
-      </c>
-      <c r="E17" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AI / Platform</t>
-        </is>
-      </c>
-      <c r="F17" s="87"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Music Quiz (expansion)</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Live - expansion 2026-10-06</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">New - expansion announced 2026-10-06. Interactive music quiz/game feature.</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Added as a newly announced 2026 product not in the original table.</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Music</t>
-        </is>
-      </c>
-      <c r="F18" s="88"/>
+          <t xml:space="preserve">Spotify Newsroom 2026-04-27</t>
+        </is>
+      </c>
     </row>
   </sheetData>
 </worksheet>
@@ -1284,529 +1364,529 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="30.00" customWidth="1"/>
-    <col min="2" max="2" width="60.00" customWidth="1"/>
+    <col min="2" max="2" width="62.00" customWidth="1"/>
     <col min="3" max="3" width="62.00" customWidth="1"/>
     <col min="4" max="4" width="14.00" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">Product</t>
         </is>
       </c>
-      <c r="B1" s="26" t="inlineStr">
+      <c r="B1" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">What It Supports</t>
         </is>
       </c>
-      <c r="C1" s="26" t="inlineStr">
+      <c r="C1" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">Source</t>
         </is>
       </c>
-      <c r="D1" s="19" t="inlineStr">
+      <c r="D1" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">As Of</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Audiobooks+ / Tiers</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">Three tiers (15/40/100 hrs); &gt;1M subs; &gt;$100M ARR; 180+ market expansion</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">newsroom.spotify.com/2026-10-07/audiobooks-global-expansion/</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Audiobooks+ / Tiers</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Audiobooks+ Family &amp; Student Plans</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">Student plans get Audiobooks+ Nov 2026 (Ireland, Belgium, Austria, Finland)</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">newsroom.spotify.com/2026-10-07/audiobooks-global-expansion/</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Personal Podcasts</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Beta launch 2026-05-07; Free and Premium worldwide; Save to Spotify</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Beta 2026-05-07; Free and Premium worldwide; Save to Spotify</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">newsroom.spotify.com/2026-05-07/personal-podcasts-launch/</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-05-07</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Creator Memberships (Podcasts)</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Announced 2026-05-21; 'soon'; portable subscriber lists; no launch</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Announced 2026-05-21; portable subscriber lists; no launch</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">newsroom.spotify.com/2026-05-21/investor-day-podcast-features-updates/</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Membership Tools (Creators)</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">Same initiative as Creator Memberships; not launched</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">newsroom.spotify.com/2026-05-21/investor-day-podcast-features-updates/</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">UMG AI Covers &amp; Remixes</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">UMG licensing 2026-05-21; consent/credit/compensation; paid add-on; no date</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">newsroom.spotify.com/2026-05-21/universal-music-group-spotify-licensing-agreements-fan-made-covers-remixes/</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">UMG AI Covers &amp; Remixes</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Merlin deal 2026-08-04; ~30k indie labels; tool still upcoming</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Merlin deal 2026-08-04; ~30k indie labels covered</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">newsroom.spotify.com/2026-08-04/merlin-spotify-licensing-agreements-fan-made-covers-remixes/</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">UMG AI Covers &amp; Remixes</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Management: no timeline, 'launch when ready' (Q2 2026 call)</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Management: no timeline, 'launch when ready'</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">billboard.com/pro/spotify-q2-2026-ai-remix-tool-has-strong-momentum/</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Reserved by Spotify</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">Launched US 2026-06-18; Role Model first artist, 19 dates</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">newsroom.spotify.com/2026-06-18/reserved-by-spotify-guide/</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-06-18</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Reserved by Spotify</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">Canada added 2026-08-17</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">iphoneincanada.ca/2026/08/17/spotifys-reserved-ticketing-presale-program-launches-in-canada/</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Reserved by Spotify</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">Share cards, setlist playlists, event hub added 2026-09-24</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">newsroom.spotify.com/2026-09-24/reserved-by-spotify-share-cards-setlists/</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Reserved by Spotify</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">Eligibility: Premium, 18+, two tickets, one-week-old account</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">help.ticketmaster.com/hc/en-us/articles/47849883539473-Reserved-by-Spotify</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Studio by Spotify Labs</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">Announced 2026-05-21; gradual rollout began 2026-07-20; macOS select markets</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">newsroom.spotify.com/2026-05-21/studio-by-spotify-labs-launch/</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Studio by Spotify Labs</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">Access terms: Premium, 18+, macOS, usage limits</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">labs.spotify.com/studio</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-15</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Creator Sponsorships (Podcasts)</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Launched; list of markets; eligibility; disclosure of metrics</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Launched; markets, eligibility, disclosure of metrics</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">newsroom.spotify.com/2026-09-17/partner-program-expansion-global/</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Creator Sponsorships (Podcasts)</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">Payouts up a third since eligibility expansion; 45%+ consumption growth</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">newsroom.spotify.com/2026-09-17/partner-program-expansion-global/</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Audiobook Creation Tools</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">Invite-only beta from June 2026; Spotify for Authors; ElevenLabs</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">newsroom.spotify.com/2026-05-21/investor-day-audiobook-features-updates/</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Audiobook Creation Tools</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">Earlier ElevenLabs ingest path (distinct from author tool)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">newsroom.spotify.com/2025-02-20/spotify-opens-up-support-for-elevenlabs-audiobook-content/</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-02-20</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prompted Playlists for Audiobooks</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prompted Playlist 14M users among first 100M exposed</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">newsroom.spotify.com/2026-05-21/investor-day-podcast-features-updates/</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Guided Adaptive Running</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referenced by management as a live differentiating feature</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spotify Q2 2026 earnings call</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Peloton Workout Videos</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fitness hub launch 2026-04-27; 1,400+ classes; Premium included</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">newsroom.spotify.com/2026-04-27/spotify-fitness-workouts-peloton/</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ask Questions About a Podcast</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">Rebranded to Talk to Spotify; beta 2026-07-14; US/Ireland/Sweden</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C23" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">newsroom.spotify.com/2026-07-14/talk-to-spotify-announcement-beta/</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D23" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-07-14</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Peloton Workout Videos</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fitness hub launch 2026-04-27; 1,400+ classes; Premium included</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">newsroom.spotify.com/2026-04-27/spotify-fitness-workouts-peloton/</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Managed Accounts (Family)</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Announced 2026-10-02 at New York event; family plan management</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">newsroom.spotify.com/2026-10-02/managed-accounts-event-new-york/</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Music Quiz (expansion)</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Expansion announced 2026-10-06; interactive music quiz/game</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">newsroom.spotify.com/2026-10-06/music-quiz-expansion/</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-06</t>
-        </is>
-      </c>
-    </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Audiobooks+ / Tiers</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Audiobook catalog 700k+ titles; listening hours +60% YoY</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Language Expansion - Authors</t>
+        </is>
+      </c>
+      <c r="B24" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Audiobooks 22 to 180+ markets by end 2026; no author-platform language product found</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">newsroom.spotify.com/2026-10-07/audiobooks-global-expansion/</t>
         </is>
@@ -1814,72 +1894,6 @@
       <c r="D24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Language Expansion - Authors</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No author-platform language product found; audiobooks 22 to 180+ markets by end 2026</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">newsroom.spotify.com/2026-10-07/audiobooks-global-expansion/</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prompted Playlists for Audiobooks</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No product by this name found; closest is AI Playlist (music only)</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">newsroom.spotify.com site search</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Guided Adaptive Running</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No running/adaptive-running feature found in newsroom or site search</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">newsroom.spotify.com site search</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-15</t>
         </is>
       </c>
     </row>
